--- a/forms/trg/Formulir_TRG_dis-intel.xlsx
+++ b/forms/trg/Formulir_TRG_dis-intel.xlsx
@@ -916,7 +916,11 @@
           <t>Dr. Zulkifli Tahir</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -945,7 +949,11 @@
           <t>Dr. Wardi</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n"/>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D6" s="12" t="n"/>
       <c r="E6" s="11" t="inlineStr">
         <is>
@@ -974,7 +982,11 @@
           <t>Tyanita Puti Marindah W, M.Inf</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n"/>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D7" s="12" t="n"/>
       <c r="E7" s="11" t="inlineStr">
         <is>
@@ -1003,7 +1015,11 @@
           <t>Muhammad Alief Fahdal Imran Oemar, M.Sc</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n"/>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D8" s="12" t="n"/>
       <c r="E8" s="11" t="inlineStr">
         <is>
@@ -1032,7 +1048,11 @@
           <t>Anugrayani Bustamin, M.T</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n"/>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D9" s="12" t="n"/>
       <c r="E9" s="11" t="inlineStr">
         <is>
@@ -1061,7 +1081,11 @@
           <t>Iqra Aswad, M.T</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n"/>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D10" s="12" t="n"/>
       <c r="E10" s="11" t="inlineStr">
         <is>
@@ -1090,7 +1114,11 @@
           <t>Arliyanti Nurdin, ST.,MT</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n"/>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D11" s="12" t="n"/>
       <c r="E11" s="11" t="inlineStr">
         <is>
@@ -1119,7 +1147,11 @@
           <t>Ts. Dr. Wan Mohd Ya'akob Wan Bejuri</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n"/>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D12" s="12" t="n"/>
       <c r="E12" s="11" t="inlineStr">
         <is>
@@ -1148,7 +1180,11 @@
           <t>Muhammad Irawan Agung</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n"/>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D13" s="12" t="n"/>
       <c r="E13" s="11" t="inlineStr">
         <is>
@@ -1177,7 +1213,11 @@
           <t>Uzaimin Nasruddin</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n"/>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D14" s="12" t="n"/>
       <c r="E14" s="11" t="inlineStr">
         <is>
